--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="71">
   <si>
     <t>Mat</t>
   </si>
@@ -76,6 +76,21 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>BALTAZARES</t>
   </si>
   <si>
@@ -91,6 +106,9 @@
     <t>RAMOS</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -115,6 +133,21 @@
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
@@ -124,12 +157,12 @@
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
     <t>MARCELINO</t>
   </si>
   <si>
@@ -142,6 +175,21 @@
     <t>ZOPIYACTLE</t>
   </si>
   <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
+    <t>EMILY</t>
+  </si>
+  <si>
     <t>IVETTE</t>
   </si>
   <si>
@@ -157,6 +205,12 @@
     <t>MARCO JOSAFAT</t>
   </si>
   <si>
+    <t>ODALYS</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
     <t>TANIA</t>
   </si>
   <si>
@@ -170,9 +224,6 @@
   </si>
   <si>
     <t>MARIA</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
   </si>
   <si>
     <t>AIDA</t>
@@ -953,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -985,22 +1036,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920260</v>
+        <v>20330051920196</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1008,22 +1059,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920270</v>
+        <v>20330051920202</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1031,22 +1082,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920272</v>
+        <v>20330051920217</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1054,22 +1105,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920238</v>
+        <v>20330051920218</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1077,22 +1128,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920278</v>
+        <v>20330051920219</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1100,22 +1151,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>18330051920393</v>
+        <v>20330051920260</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1123,22 +1174,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920115</v>
+        <v>20330051920270</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1146,22 +1197,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920116</v>
+        <v>20330051920272</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1169,22 +1220,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920118</v>
+        <v>19330051920238</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1192,22 +1243,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920121</v>
+        <v>20330051920278</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1215,16 +1266,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920124</v>
+        <v>20330051920127</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1238,16 +1289,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920125</v>
+        <v>20330051920387</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1261,13 +1312,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920153</v>
+        <v>18330051920393</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1276,7 +1330,165 @@
         <v>12</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920115</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920116</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920118</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920121</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920124</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920125</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920153</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="79">
   <si>
     <t>Mat</t>
   </si>
@@ -79,36 +79,39 @@
     <t>ESTEVEZ</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>DE LA TEJA</t>
   </si>
   <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
@@ -130,12 +133,36 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
@@ -148,21 +175,6 @@
     <t>GALEOTE</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
     <t>MARCELINO</t>
   </si>
   <si>
@@ -175,9 +187,39 @@
     <t>ZOPIYACTLE</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>ERICK DE JESUS</t>
   </si>
   <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>IVETTE</t>
+  </si>
+  <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>ODALYS</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
     <t>ITZEL</t>
   </si>
   <si>
@@ -190,27 +232,6 @@
     <t>EMILY</t>
   </si>
   <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
     <t>TANIA</t>
   </si>
   <si>
@@ -227,6 +248,9 @@
   </si>
   <si>
     <t>AIDA</t>
+  </si>
+  <si>
+    <t>CONSTANZA XIMENA</t>
   </si>
   <si>
     <t>KIMBERLY</t>
@@ -1004,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1042,10 +1066,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1059,16 +1083,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920202</v>
+        <v>20330051920214</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1082,22 +1106,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920217</v>
+        <v>20330051920260</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1105,22 +1129,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920218</v>
+        <v>20330051920270</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1128,22 +1152,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920219</v>
+        <v>20330051920272</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1151,16 +1175,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920260</v>
+        <v>19330051920238</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1174,16 +1198,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920270</v>
+        <v>20330051920278</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1197,22 +1221,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920272</v>
+        <v>20330051920127</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1220,22 +1244,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920238</v>
+        <v>20330051920387</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1243,91 +1267,91 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920278</v>
+        <v>20330051920063</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920127</v>
+        <v>20330051920202</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920387</v>
+        <v>20330051920217</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>18330051920393</v>
+        <v>20330051920218</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1335,22 +1359,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920115</v>
+        <v>20330051920219</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1358,16 +1382,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920116</v>
+        <v>18330051920393</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1381,16 +1405,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920118</v>
+        <v>20330051920115</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1404,16 +1428,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920121</v>
+        <v>20330051920116</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1427,16 +1451,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920124</v>
+        <v>20330051920118</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1450,16 +1474,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920125</v>
+        <v>20330051920121</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1473,13 +1497,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920153</v>
+        <v>20330051920124</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="C21" t="s">
+        <v>44</v>
       </c>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1488,6 +1515,72 @@
         <v>12</v>
       </c>
       <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920125</v>
+      </c>
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920151</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>56</v>
+      </c>
+      <c r="D23" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920153</v>
+      </c>
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="64">
   <si>
     <t>Mat</t>
   </si>
@@ -76,15 +76,12 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ESTEVEZ</t>
+    <t>ROSETE</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -97,57 +94,39 @@
     <t>RAMOS</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CONGUILLO</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>MORENO</t>
+    <t>SALAS</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
     <t>DIAZ</t>
   </si>
   <si>
@@ -157,48 +136,39 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>FERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>SALAZAR</t>
   </si>
   <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
+    <t>VICTOR GAEL</t>
   </si>
   <si>
     <t>ALEJANDRA</t>
   </si>
   <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
     <t>ELIAS ALONSO</t>
   </si>
   <si>
@@ -211,46 +181,31 @@
     <t>MARCO JOSAFAT</t>
   </si>
   <si>
+    <t>CONSTANZA XIMENA</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>TANIA</t>
+  </si>
+  <si>
+    <t>MELANIE NAOMI</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>VALENTIN</t>
+  </si>
+  <si>
     <t>ODALYS</t>
   </si>
   <si>
     <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>ALISSON FERNANDA</t>
-  </si>
-  <si>
-    <t>EMILY</t>
-  </si>
-  <si>
-    <t>TANIA</t>
-  </si>
-  <si>
-    <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>CONSUELO DALILA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
   </si>
   <si>
     <t>KIMBERLY</t>
@@ -797,16 +752,19 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>45</v>
+      </c>
+      <c r="H2">
+        <v>5.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -820,16 +778,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>69.23</v>
+      </c>
+      <c r="H3">
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -843,16 +804,19 @@
         <v>17</v>
       </c>
       <c r="D4">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>70.59</v>
+      </c>
+      <c r="H4">
+        <v>5.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -866,16 +830,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>61.29</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -931,16 +898,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -957,16 +924,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>65.38</v>
+        <v>69.23</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -983,16 +950,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>58.82</v>
+        <v>70.59</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1009,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>58.06</v>
+        <v>61.29</v>
       </c>
       <c r="H5">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -1028,7 +995,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1060,22 +1027,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920196</v>
+        <v>20330051920063</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1089,10 +1056,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1106,16 +1073,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920260</v>
+        <v>20330051920270</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1129,16 +1096,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920270</v>
+        <v>20330051920272</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1152,16 +1119,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920272</v>
+        <v>19330051920238</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1175,16 +1142,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920238</v>
+        <v>20330051920278</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1198,22 +1165,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920278</v>
+        <v>20330051920151</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1221,68 +1188,68 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920127</v>
+        <v>20330051920202</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920387</v>
+        <v>20330051920217</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920063</v>
+        <v>18330051920393</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1290,22 +1257,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920202</v>
+        <v>20330051920115</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1313,22 +1280,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920217</v>
+        <v>20330051920116</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1336,22 +1303,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920218</v>
+        <v>19330051920427</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1359,22 +1326,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920219</v>
+        <v>20330051920127</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="D15" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1382,16 +1349,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>18330051920393</v>
+        <v>20330051920140</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1405,16 +1372,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920115</v>
+        <v>20330051920387</v>
       </c>
       <c r="B17" t="s">
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1428,16 +1395,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920116</v>
+        <v>20330051920153</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
       </c>
-      <c r="C18" t="s">
-        <v>54</v>
-      </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1446,141 +1410,6 @@
         <v>12</v>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920118</v>
-      </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920121</v>
-      </c>
-      <c r="B20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920124</v>
-      </c>
-      <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D21" t="s">
-        <v>67</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920125</v>
-      </c>
-      <c r="B22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>20330051920151</v>
-      </c>
-      <c r="B23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C23" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" t="s">
-        <v>77</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920153</v>
-      </c>
-      <c r="B24" t="s">
-        <v>39</v>
-      </c>
-      <c r="D24" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="67">
   <si>
     <t>Mat</t>
   </si>
@@ -76,6 +76,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>ROSETE</t>
   </si>
   <si>
@@ -121,6 +124,9 @@
     <t>TRUJILLO</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>SALAS</t>
   </si>
   <si>
@@ -161,6 +167,9 @@
   </si>
   <si>
     <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>JESUS ISRAEL</t>
   </si>
   <si>
     <t>VICTOR GAEL</t>
@@ -995,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1027,16 +1036,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920063</v>
+        <v>19330051920051</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1050,22 +1059,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920214</v>
+        <v>20330051920063</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1073,22 +1082,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920270</v>
+        <v>20330051920214</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1096,16 +1105,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920272</v>
+        <v>20330051920270</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1119,16 +1128,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920238</v>
+        <v>20330051920272</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1142,16 +1151,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920278</v>
+        <v>19330051920238</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1165,22 +1174,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920151</v>
+        <v>20330051920278</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1188,39 +1197,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920202</v>
+        <v>20330051920151</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920217</v>
+        <v>20330051920202</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1234,22 +1243,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>18330051920393</v>
+        <v>20330051920217</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1257,16 +1266,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920115</v>
+        <v>18330051920393</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1280,16 +1289,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920116</v>
+        <v>20330051920115</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1303,16 +1312,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920427</v>
+        <v>20330051920116</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1326,16 +1335,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920127</v>
+        <v>19330051920427</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1349,16 +1358,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920140</v>
+        <v>20330051920127</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1372,16 +1381,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920387</v>
+        <v>20330051920140</v>
       </c>
       <c r="B17" t="s">
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1395,13 +1404,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920153</v>
+        <v>20330051920387</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
       </c>
+      <c r="C18" t="s">
+        <v>49</v>
+      </c>
       <c r="D18" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1410,6 +1422,26 @@
         <v>12</v>
       </c>
       <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920153</v>
+      </c>
+      <c r="B19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
@@ -133,6 +133,9 @@
     <t>HUERTA</t>
   </si>
   <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
     <t>DIAZ</t>
   </si>
   <si>
@@ -148,9 +151,6 @@
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
     <t>MARCELINO</t>
   </si>
   <si>
@@ -178,6 +178,9 @@
     <t>ALEJANDRA</t>
   </si>
   <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
     <t>ELIAS ALONSO</t>
   </si>
   <si>
@@ -194,9 +197,6 @@
   </si>
   <si>
     <t>ITZEL</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
   </si>
   <si>
     <t>TANIA</t>
@@ -1105,10 +1105,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920270</v>
+        <v>20330051920217</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
         <v>38</v>
@@ -1120,7 +1120,7 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920272</v>
+        <v>20330051920270</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
         <v>39</v>
@@ -1151,13 +1151,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920238</v>
+        <v>20330051920272</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
         <v>55</v>
@@ -1174,13 +1174,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920278</v>
+        <v>19330051920238</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1197,10 +1197,10 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920151</v>
+        <v>20330051920278</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
         <v>41</v>
@@ -1212,7 +1212,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1220,10 +1220,10 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920202</v>
+        <v>20330051920151</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>42</v>
@@ -1235,18 +1235,18 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920217</v>
+        <v>20330051920202</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
         <v>43</v>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="64">
   <si>
     <t>Mat</t>
   </si>
@@ -97,9 +97,6 @@
     <t>RAMOS</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
@@ -145,9 +142,6 @@
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
@@ -191,9 +185,6 @@
   </si>
   <si>
     <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
   </si>
   <si>
     <t>ITZEL</t>
@@ -1004,7 +995,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1042,10 +1033,10 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1065,10 +1056,10 @@
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1088,10 +1079,10 @@
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1111,10 +1102,10 @@
         <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1134,10 +1125,10 @@
         <v>22</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1157,10 +1148,10 @@
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1183,7 +1174,7 @@
         <v>21</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1203,10 +1194,10 @@
         <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1220,45 +1211,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920151</v>
+        <v>20330051920202</v>
       </c>
       <c r="B10" t="s">
         <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920202</v>
+        <v>18330051920393</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1266,16 +1257,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>18330051920393</v>
+        <v>20330051920115</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1289,16 +1280,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920115</v>
+        <v>20330051920116</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1312,16 +1303,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920116</v>
+        <v>19330051920427</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1335,16 +1326,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920427</v>
+        <v>20330051920127</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1358,16 +1349,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920127</v>
+        <v>20330051920140</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1381,16 +1372,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920140</v>
+        <v>20330051920387</v>
       </c>
       <c r="B17" t="s">
         <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1404,16 +1395,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920387</v>
+        <v>20330051920153</v>
       </c>
       <c r="B18" t="s">
         <v>33</v>
       </c>
-      <c r="C18" t="s">
-        <v>49</v>
-      </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1422,26 +1410,6 @@
         <v>12</v>
       </c>
       <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920153</v>
-      </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -76,139 +76,79 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>FERNANDEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>JESUS URIEL</t>
   </si>
   <si>
     <t>IRVING JAIR</t>
   </si>
   <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>TANIA</t>
-  </si>
-  <si>
-    <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>VALENTIN</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>CONSTANZA XIMENA</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
   </si>
 </sst>
 </file>
@@ -898,16 +838,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -924,16 +864,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>69.23</v>
+        <v>84.62</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -950,16 +890,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>70.59</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -976,16 +916,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>61.29</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H5">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -995,7 +935,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1027,22 +967,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920051</v>
+        <v>20330051920200</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1050,22 +990,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920063</v>
+        <v>20330051920259</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1073,22 +1013,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920214</v>
+        <v>19330051920238</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1096,22 +1036,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920217</v>
+        <v>20330051920132</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1119,22 +1059,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920270</v>
+        <v>20330051920151</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1142,274 +1082,93 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920272</v>
+        <v>20330051920082</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920238</v>
+        <v>20330051920196</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920278</v>
+        <v>20330051920126</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920202</v>
+        <v>20330051920168</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>18330051920393</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920115</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920116</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920427</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920127</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920140</v>
-      </c>
-      <c r="B16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>20330051920387</v>
-      </c>
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920153</v>
-      </c>
-      <c r="B18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" t="s">
-        <v>63</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="47">
   <si>
     <t>Mat</t>
   </si>
@@ -76,15 +76,18 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
     <t>GALVEZ</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -103,12 +106,15 @@
     <t>HUESCA</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
     <t>COLOHUA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>NOYOLA</t>
   </si>
   <si>
@@ -124,13 +130,16 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
     <t>ANTONIO ABIDAN</t>
   </si>
   <si>
     <t>JESUS URIEL</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
   </si>
   <si>
     <t>MARIA JOSE</t>
@@ -935,7 +944,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -967,22 +976,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920200</v>
+        <v>20330051920071</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -990,22 +999,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920259</v>
+        <v>20330051920073</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1013,22 +1022,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920238</v>
+        <v>20330051920200</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1036,22 +1045,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920132</v>
+        <v>20330051920259</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1059,16 +1068,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920151</v>
+        <v>20330051920132</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1082,45 +1091,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920082</v>
+        <v>20330051920151</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920196</v>
+        <v>20330051920082</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1128,22 +1137,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920126</v>
+        <v>20330051920196</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1151,16 +1160,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920168</v>
+        <v>20330051920126</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1169,6 +1178,29 @@
         <v>12</v>
       </c>
       <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920168</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
+++ b/docentes/Gaspar Velazco Juan Francisco - Estadisticos 20222.xlsx
@@ -91,21 +91,21 @@
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUESCA</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUESCA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -118,18 +118,18 @@
     <t>NOYOLA</t>
   </si>
   <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>MARCO ANTONIO</t>
   </si>
   <si>
@@ -145,19 +145,19 @@
     <t>MARIA JOSE</t>
   </si>
   <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>ALDAIR OMAR</t>
+  </si>
+  <si>
     <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>ALDAIR OMAR</t>
   </si>
 </sst>
 </file>
@@ -1091,7 +1091,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920151</v>
+        <v>20330051920082</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
@@ -1106,15 +1106,15 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920082</v>
+        <v>20330051920196</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
@@ -1129,7 +1129,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -1137,13 +1137,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920196</v>
+        <v>20330051920126</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D9" t="s">
         <v>44</v>
@@ -1152,7 +1152,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -1160,13 +1160,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920126</v>
+        <v>20330051920168</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
         <v>45</v>
@@ -1183,7 +1183,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920168</v>
+        <v>20330051920151</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
